--- a/EKG_Kalite_Yönetim_Sistemi/10_Değişiklik ve Geçici Proses Kontrolü/01_MC1 - Talep, Etki ve Müşteri Onayı/EKG-PRJ-FRM-28_degisiklik_talebi_ve_musteri_onay_formu__excel_duzeni.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/10_Değişiklik ve Geçici Proses Kontrolü/01_MC1 - Talep, Etki ve Müşteri Onayı/EKG-PRJ-FRM-28_degisiklik_talebi_ve_musteri_onay_formu__excel_duzeni.xlsx
@@ -1105,7 +1105,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-28&amp;C&amp;"Arial,Regular"&amp;11Değişiklik Talebi ve Müşteri Onay Formu - Excel Düzeni</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 23.09.2026
+Revizyon nedeni: Müşteri kararı ve izin kapsamı açık alanlarla izlenir hale getirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
